--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2470"/>
+  <dimension ref="A1:L2480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103066,6 +103066,406 @@
         </is>
       </c>
     </row>
+    <row r="2471">
+      <c r="A2471" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2471" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2471" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2471" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="F2471" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="G2471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2471" t="inlineStr"/>
+      <c r="I2471" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2471" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2471" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="L2471" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2472" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2472" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2472" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="F2472" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="G2472" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2472" t="inlineStr"/>
+      <c r="I2472" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2472" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2472" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="L2472" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2473" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2473" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2473" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F2473" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="G2473" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2473" t="inlineStr"/>
+      <c r="I2473" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2473" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2473" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="L2473" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2474" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2474" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2474" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F2474" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G2474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2474" t="inlineStr"/>
+      <c r="I2474" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2474" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2474" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="L2474" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2475" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2475" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2475" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F2475" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G2475" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2475" t="inlineStr"/>
+      <c r="I2475" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2475" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2475" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L2475" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2476" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2476" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2476" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="F2476" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="G2476" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2476" t="inlineStr"/>
+      <c r="I2476" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2476" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2476" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="L2476" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2477" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2477" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2477" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="F2477" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="G2477" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2477" t="inlineStr"/>
+      <c r="I2477" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2477" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2477" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="L2477" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2478" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2478" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2478" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F2478" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="G2478" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2478" t="inlineStr"/>
+      <c r="I2478" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2478" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2478" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="L2478" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2479" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2479" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2479" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F2479" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G2479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2479" t="inlineStr"/>
+      <c r="I2479" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2479" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2479" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="L2479" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2480" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2480" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2480" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F2480" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G2480" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2480" t="inlineStr"/>
+      <c r="I2480" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2480" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2480" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="L2480" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2480"/>
+  <dimension ref="A1:L2485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103466,6 +103466,206 @@
         </is>
       </c>
     </row>
+    <row r="2481">
+      <c r="A2481" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2481" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2481" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2481" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="F2481" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="G2481" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2481" t="inlineStr"/>
+      <c r="I2481" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2481" t="n">
+        <v>198</v>
+      </c>
+      <c r="K2481" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="L2481" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2482" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2482" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2482" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2482" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="G2482" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2482" t="inlineStr"/>
+      <c r="I2482" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J2482" t="n">
+        <v>154</v>
+      </c>
+      <c r="K2482" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="L2482" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2483" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2483" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2483" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="F2483" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="G2483" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2483" t="inlineStr"/>
+      <c r="I2483" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2483" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2483" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="L2483" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2484" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2484" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2484" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F2484" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="G2484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2484" t="inlineStr"/>
+      <c r="I2484" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2484" t="n">
+        <v>66</v>
+      </c>
+      <c r="K2484" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L2484" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2485" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2485" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="F2485" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="G2485" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2485" t="inlineStr"/>
+      <c r="I2485" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2485" t="n">
+        <v>113</v>
+      </c>
+      <c r="K2485" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="L2485" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2485"/>
+  <dimension ref="A1:L2490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103666,6 +103666,206 @@
         </is>
       </c>
     </row>
+    <row r="2486">
+      <c r="A2486" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2486" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2486" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F2486" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="G2486" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2486" t="inlineStr"/>
+      <c r="I2486" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2486" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2486" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="L2486" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2487" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2487" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2487" t="inlineStr"/>
+      <c r="I2487" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J2487" t="n">
+        <v>154</v>
+      </c>
+      <c r="K2487" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="L2487" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2488" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="G2488" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2488" t="inlineStr"/>
+      <c r="I2488" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2488" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2488" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="L2488" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2489" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="G2489" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2489" t="inlineStr"/>
+      <c r="I2489" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2489" t="n">
+        <v>81</v>
+      </c>
+      <c r="K2489" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="L2489" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2490" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G2490" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2490" t="inlineStr"/>
+      <c r="I2490" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2490" t="n">
+        <v>111</v>
+      </c>
+      <c r="K2490" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="L2490" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2490"/>
+  <dimension ref="A1:L2495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103866,6 +103866,206 @@
         </is>
       </c>
     </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2491" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="G2491" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2491" t="inlineStr"/>
+      <c r="I2491" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2491" t="n">
+        <v>195</v>
+      </c>
+      <c r="K2491" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="L2491" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2492" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G2492" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2492" t="inlineStr"/>
+      <c r="I2492" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2492" t="n">
+        <v>151</v>
+      </c>
+      <c r="K2492" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="L2492" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2493" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="G2493" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H2493" t="inlineStr"/>
+      <c r="I2493" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2493" t="n">
+        <v>31</v>
+      </c>
+      <c r="K2493" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="L2493" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2494" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="G2494" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2494" t="inlineStr"/>
+      <c r="I2494" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2494" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2494" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L2494" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2495" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="G2495" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2495" t="inlineStr"/>
+      <c r="I2495" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2495" t="n">
+        <v>64</v>
+      </c>
+      <c r="K2495" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="L2495" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2495"/>
+  <dimension ref="A1:L2500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104066,6 +104066,206 @@
         </is>
       </c>
     </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2496" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="G2496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2496" t="inlineStr"/>
+      <c r="I2496" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J2496" t="n">
+        <v>189</v>
+      </c>
+      <c r="K2496" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="L2496" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2497" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="G2497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2497" t="inlineStr"/>
+      <c r="I2497" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J2497" t="n">
+        <v>167</v>
+      </c>
+      <c r="K2497" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="L2497" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2498" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="G2498" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2498" t="inlineStr"/>
+      <c r="I2498" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J2498" t="n">
+        <v>58</v>
+      </c>
+      <c r="K2498" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L2498" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2499" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G2499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2499" t="inlineStr"/>
+      <c r="I2499" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J2499" t="n">
+        <v>92</v>
+      </c>
+      <c r="K2499" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="L2499" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2500" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="G2500" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2500" t="inlineStr"/>
+      <c r="I2500" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2500" t="n">
+        <v>125</v>
+      </c>
+      <c r="K2500" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="L2500" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2500"/>
+  <dimension ref="A1:L2505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104266,6 +104266,206 @@
         </is>
       </c>
     </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2501" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="G2501" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2501" t="inlineStr"/>
+      <c r="I2501" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J2501" t="n">
+        <v>196</v>
+      </c>
+      <c r="K2501" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="L2501" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2502" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2502" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2502" t="inlineStr"/>
+      <c r="I2502" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J2502" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2502" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="L2502" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2503" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="G2503" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2503" t="inlineStr"/>
+      <c r="I2503" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J2503" t="n">
+        <v>49</v>
+      </c>
+      <c r="K2503" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L2503" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2504" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="G2504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2504" t="inlineStr"/>
+      <c r="I2504" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J2504" t="n">
+        <v>101</v>
+      </c>
+      <c r="K2504" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="L2504" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2505" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G2505" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2505" t="inlineStr"/>
+      <c r="I2505" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J2505" t="n">
+        <v>121</v>
+      </c>
+      <c r="K2505" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="L2505" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2505"/>
+  <dimension ref="A1:L2510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104466,6 +104466,206 @@
         </is>
       </c>
     </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2506" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="G2506" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2506" t="inlineStr"/>
+      <c r="I2506" t="n">
+        <v>24</v>
+      </c>
+      <c r="J2506" t="n">
+        <v>187</v>
+      </c>
+      <c r="K2506" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="L2506" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2507" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="G2507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2507" t="inlineStr"/>
+      <c r="I2507" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2507" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2507" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="L2507" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2508" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="G2508" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2508" t="inlineStr"/>
+      <c r="I2508" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2508" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2508" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="L2508" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2509" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="G2509" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2509" t="inlineStr"/>
+      <c r="I2509" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2509" t="n">
+        <v>86</v>
+      </c>
+      <c r="K2509" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="L2509" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2510" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G2510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2510" t="inlineStr"/>
+      <c r="I2510" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2510" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2510" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="L2510" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2510"/>
+  <dimension ref="A1:L2515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104666,6 +104666,206 @@
         </is>
       </c>
     </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2511" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="G2511" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2511" t="inlineStr"/>
+      <c r="I2511" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J2511" t="n">
+        <v>191</v>
+      </c>
+      <c r="K2511" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="L2511" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2512" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="G2512" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2512" t="inlineStr"/>
+      <c r="I2512" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J2512" t="n">
+        <v>168</v>
+      </c>
+      <c r="K2512" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="L2512" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2513" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="G2513" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2513" t="inlineStr"/>
+      <c r="I2513" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J2513" t="n">
+        <v>44</v>
+      </c>
+      <c r="K2513" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="L2513" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2514" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G2514" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2514" t="inlineStr"/>
+      <c r="I2514" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J2514" t="n">
+        <v>86</v>
+      </c>
+      <c r="K2514" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="L2514" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2515" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G2515" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2515" t="inlineStr"/>
+      <c r="I2515" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2515" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2515" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L2515" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2515"/>
+  <dimension ref="A1:L2520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104866,6 +104866,206 @@
         </is>
       </c>
     </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2516" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="G2516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2516" t="inlineStr"/>
+      <c r="I2516" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J2516" t="n">
+        <v>114</v>
+      </c>
+      <c r="K2516" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="L2516" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2517" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="G2517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2517" t="inlineStr"/>
+      <c r="I2517" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J2517" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2517" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="L2517" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2518" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="G2518" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2518" t="inlineStr"/>
+      <c r="I2518" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="J2518" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2518" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="L2518" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2519" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G2519" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2519" t="inlineStr"/>
+      <c r="I2519" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J2519" t="n">
+        <v>104</v>
+      </c>
+      <c r="K2519" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="L2519" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2520" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="G2520" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2520" t="inlineStr"/>
+      <c r="I2520" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J2520" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2520" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="L2520" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2520"/>
+  <dimension ref="A1:L2525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105066,6 +105066,206 @@
         </is>
       </c>
     </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2521" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="G2521" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2521" t="inlineStr"/>
+      <c r="I2521" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2521" t="n">
+        <v>193</v>
+      </c>
+      <c r="K2521" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="L2521" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2522" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="G2522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2522" t="inlineStr"/>
+      <c r="I2522" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J2522" t="n">
+        <v>165</v>
+      </c>
+      <c r="K2522" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L2522" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2523" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="G2523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2523" t="inlineStr"/>
+      <c r="I2523" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J2523" t="n">
+        <v>44</v>
+      </c>
+      <c r="K2523" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="L2523" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2524" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="G2524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2524" t="inlineStr"/>
+      <c r="I2524" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J2524" t="n">
+        <v>84</v>
+      </c>
+      <c r="K2524" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="L2524" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2525" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>63</v>
+      </c>
+      <c r="G2525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2525" t="inlineStr"/>
+      <c r="I2525" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J2525" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2525" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="L2525" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2525"/>
+  <dimension ref="A1:L2530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105266,6 +105266,206 @@
         </is>
       </c>
     </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2526" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="G2526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2526" t="inlineStr"/>
+      <c r="I2526" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2526" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2526" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="L2526" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2527" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="G2527" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2527" t="inlineStr"/>
+      <c r="I2527" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2527" t="n">
+        <v>135</v>
+      </c>
+      <c r="K2527" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="L2527" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2528" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="G2528" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2528" t="inlineStr"/>
+      <c r="I2528" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2528" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2528" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L2528" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2529" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="G2529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2529" t="inlineStr"/>
+      <c r="I2529" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2529" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2529" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="L2529" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2530" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G2530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2530" t="inlineStr"/>
+      <c r="I2530" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J2530" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2530" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="L2530" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2530"/>
+  <dimension ref="A1:L2535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105466,6 +105466,206 @@
         </is>
       </c>
     </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2531" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="G2531" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2531" t="inlineStr"/>
+      <c r="I2531" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J2531" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2531" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="L2531" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2532" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="G2532" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2532" t="inlineStr"/>
+      <c r="I2532" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J2532" t="n">
+        <v>117</v>
+      </c>
+      <c r="K2532" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L2532" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2533" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2533" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2533" t="inlineStr"/>
+      <c r="I2533" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J2533" t="n">
+        <v>59</v>
+      </c>
+      <c r="K2533" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="L2533" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2534" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="G2534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2534" t="inlineStr"/>
+      <c r="I2534" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J2534" t="n">
+        <v>86</v>
+      </c>
+      <c r="K2534" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="L2534" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2535" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="G2535" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2535" t="inlineStr"/>
+      <c r="I2535" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J2535" t="n">
+        <v>124</v>
+      </c>
+      <c r="K2535" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="L2535" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2535"/>
+  <dimension ref="A1:L2540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105666,6 +105666,206 @@
         </is>
       </c>
     </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2536" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G2536" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2536" t="inlineStr"/>
+      <c r="I2536" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2536" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2536" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L2536" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2537" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="G2537" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H2537" t="inlineStr"/>
+      <c r="I2537" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2537" t="n">
+        <v>132</v>
+      </c>
+      <c r="K2537" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="L2537" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2538" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="G2538" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2538" t="inlineStr"/>
+      <c r="I2538" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2538" t="n">
+        <v>44</v>
+      </c>
+      <c r="K2538" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L2538" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2539" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2539" t="inlineStr"/>
+      <c r="I2539" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2539" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2539" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="L2539" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2540" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="G2540" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2540" t="inlineStr"/>
+      <c r="I2540" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2540" t="n">
+        <v>122</v>
+      </c>
+      <c r="K2540" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L2540" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2540"/>
+  <dimension ref="A1:L2545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105866,6 +105866,206 @@
         </is>
       </c>
     </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2541" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="G2541" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2541" t="inlineStr"/>
+      <c r="I2541" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2541" t="n">
+        <v>59</v>
+      </c>
+      <c r="K2541" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="L2541" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2542" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G2542" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2542" t="inlineStr"/>
+      <c r="I2542" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2542" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2542" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="L2542" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2543" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G2543" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H2543" t="inlineStr"/>
+      <c r="I2543" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2543" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2543" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="L2543" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2544" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>69</v>
+      </c>
+      <c r="G2544" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2544" t="inlineStr"/>
+      <c r="I2544" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2544" t="n">
+        <v>79</v>
+      </c>
+      <c r="K2544" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="L2544" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2545" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="G2545" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2545" t="inlineStr"/>
+      <c r="I2545" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2545" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2545" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="L2545" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2545"/>
+  <dimension ref="A1:L2550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106066,6 +106066,206 @@
         </is>
       </c>
     </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2546" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G2546" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2546" t="inlineStr"/>
+      <c r="I2546" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J2546" t="n">
+        <v>190</v>
+      </c>
+      <c r="K2546" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="L2546" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2547" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="G2547" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2547" t="inlineStr"/>
+      <c r="I2547" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J2547" t="n">
+        <v>174</v>
+      </c>
+      <c r="K2547" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="L2547" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2548" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G2548" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2548" t="inlineStr"/>
+      <c r="I2548" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J2548" t="n">
+        <v>59</v>
+      </c>
+      <c r="K2548" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="L2548" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2549" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2549" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2549" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2549" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="G2549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2549" t="inlineStr"/>
+      <c r="I2549" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J2549" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2549" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="L2549" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2550" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="G2550" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2550" t="inlineStr"/>
+      <c r="I2550" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J2550" t="n">
+        <v>106</v>
+      </c>
+      <c r="K2550" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="L2550" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2550"/>
+  <dimension ref="A1:L2555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106266,6 +106266,206 @@
         </is>
       </c>
     </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2551" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G2551" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2551" t="inlineStr"/>
+      <c r="I2551" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="J2551" t="n">
+        <v>181</v>
+      </c>
+      <c r="K2551" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="L2551" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2552" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2552" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2552" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="G2552" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H2552" t="inlineStr"/>
+      <c r="I2552" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J2552" t="n">
+        <v>158</v>
+      </c>
+      <c r="K2552" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L2552" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2553" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="G2553" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2553" t="inlineStr"/>
+      <c r="I2553" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J2553" t="n">
+        <v>58</v>
+      </c>
+      <c r="K2553" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="L2553" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2554" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="G2554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2554" t="inlineStr"/>
+      <c r="I2554" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="J2554" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2554" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="L2554" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2555" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="G2555" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2555" t="inlineStr"/>
+      <c r="I2555" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J2555" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2555" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="L2555" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2555"/>
+  <dimension ref="A1:L2560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106466,6 +106466,206 @@
         </is>
       </c>
     </row>
+    <row r="2556">
+      <c r="A2556" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2556" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2556" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2556" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="G2556" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2556" t="inlineStr"/>
+      <c r="I2556" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2556" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2556" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L2556" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2557" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="G2557" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H2557" t="inlineStr"/>
+      <c r="I2557" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2557" t="n">
+        <v>178</v>
+      </c>
+      <c r="K2557" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="L2557" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2558" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2558" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2558" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="G2558" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2558" t="inlineStr"/>
+      <c r="I2558" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2558" t="n">
+        <v>53</v>
+      </c>
+      <c r="K2558" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="L2558" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2559" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G2559" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2559" t="inlineStr"/>
+      <c r="I2559" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2559" t="n">
+        <v>91</v>
+      </c>
+      <c r="K2559" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="L2559" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2560" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="G2560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2560" t="inlineStr"/>
+      <c r="I2560" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J2560" t="n">
+        <v>118</v>
+      </c>
+      <c r="K2560" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L2560" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/data_suhu_lama.xlsx
+++ b/data/data_suhu_lama.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2560"/>
+  <dimension ref="A1:L2565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106666,6 +106666,206 @@
         </is>
       </c>
     </row>
+    <row r="2561">
+      <c r="A2561" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>KEDIRI</t>
+        </is>
+      </c>
+      <c r="C2561" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2561" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2561" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="F2561" t="n">
+        <v>68.34999999999999</v>
+      </c>
+      <c r="G2561" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2561" t="inlineStr"/>
+      <c r="I2561" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J2561" t="n">
+        <v>190</v>
+      </c>
+      <c r="K2561" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="L2561" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>MALANG</t>
+        </is>
+      </c>
+      <c r="C2562" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2562" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2562" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G2562" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2562" t="inlineStr"/>
+      <c r="I2562" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="J2562" t="n">
+        <v>165</v>
+      </c>
+      <c r="K2562" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="L2562" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>PASURUAN</t>
+        </is>
+      </c>
+      <c r="C2563" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2563" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2563" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F2563" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="G2563" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2563" t="inlineStr"/>
+      <c r="I2563" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J2563" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2563" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="L2563" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>SIDOARJO</t>
+        </is>
+      </c>
+      <c r="C2564" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="G2564" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2564" t="inlineStr"/>
+      <c r="I2564" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2564" t="n">
+        <v>90</v>
+      </c>
+      <c r="K2564" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L2564" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>SURABAYA</t>
+        </is>
+      </c>
+      <c r="C2565" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2565" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2565" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G2565" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2565" t="inlineStr"/>
+      <c r="I2565" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J2565" t="n">
+        <v>119</v>
+      </c>
+      <c r="K2565" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="L2565" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
